--- a/XLibur.Tests/Resource/Other/RichText/kanji-with-new-line-output.xlsx
+++ b/XLibur.Tests/Resource/Other/RichText/kanji-with-new-line-output.xlsx
@@ -432,9 +432,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="B2:B3"/>
   <x:sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <x:sheetData>
@@ -446,10 +443,7 @@
     </x:row>
   </x:sheetData>
   <x:phoneticPr fontId="1"/>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="9" scale="100" pageOrder="downThenOver" orientation="portrait" blackAndWhite="0" draft="0" cellComments="none" errors="displayed" r:id="rId1"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </x:worksheet>
 </file>
--- a/XLibur.Tests/Resource/Other/RichText/kanji-with-new-line-output.xlsx
+++ b/XLibur.Tests/Resource/Other/RichText/kanji-with-new-line-output.xlsx
@@ -444,6 +444,6 @@
   </x:sheetData>
   <x:phoneticPr fontId="1"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <x:pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967294" r:id="rId1"/>
 </x:worksheet>
 </file>
--- a/XLibur.Tests/Resource/Other/RichText/kanji-with-new-line-output.xlsx
+++ b/XLibur.Tests/Resource/Other/RichText/kanji-with-new-line-output.xlsx
@@ -28,7 +28,7 @@
     <x:rPh sb="1" eb="3">
       <x:t>カンジ</x:t>
     </x:rPh>
-    <x:phoneticPr fontId="0"/>
+    <x:phoneticPr fontId="2"/>
   </x:si>
 </x:sst>
 </file>
